--- a/data/processed/harmonization/Base_cations__Exchangeable_magnesium/10.15485_1960313/10.15485_1960313_soil_Base_cations__Exchangeable_magnesium.xlsx
+++ b/data/processed/harmonization/Base_cations__Exchangeable_magnesium/10.15485_1960313/10.15485_1960313_soil_Base_cations__Exchangeable_magnesium.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="53" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="6" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
@@ -518,12 +518,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>IEEXG001N</t>
+          <t>upland:IEEXG001N</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
@@ -570,12 +570,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>IEEXG001Q</t>
+          <t>transition:IEEXG001Q</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
@@ -622,12 +622,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>IEEXG001K</t>
+          <t>wetland:IEEXG001K</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
@@ -674,12 +674,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>IEEXG003F</t>
+          <t>upland:IEEXG003F</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr"/>
@@ -726,12 +726,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>IEEXG003I</t>
+          <t>transition:IEEXG003I</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -778,12 +778,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>IEEXG003C</t>
+          <t>wetland:IEEXG003C</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr"/>
@@ -830,12 +830,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>IEEXG003V</t>
+          <t>upland:IEEXG003V</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr"/>
@@ -882,12 +882,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>IEEXG003Y</t>
+          <t>transition:IEEXG003Y</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>IEEXG003S</t>
+          <t>wetland:IEEXG003S</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr"/>
@@ -986,12 +986,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>IEEXG004B</t>
+          <t>upland:IEEXG004B</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr"/>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>IEEXG004E</t>
+          <t>transition:IEEXG004E</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr"/>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0048</t>
+          <t>wetland:IEEXG0048</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr"/>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>IEEXG004R</t>
+          <t>upland:IEEXG004R</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr"/>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>IEEXG004U</t>
+          <t>transition:IEEXG004U</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr"/>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>IEEXG004O</t>
+          <t>wetland:IEEXG004O</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr"/>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0054</t>
+          <t>wetland:IEEXG0054</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr"/>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>IEEXG005N</t>
+          <t>upland:IEEXG005N</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr"/>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>IEEXG005Q</t>
+          <t>transition:IEEXG005Q</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr"/>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>IEEXG005K</t>
+          <t>wetland:IEEXG005K</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr"/>
@@ -1506,12 +1506,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0060</t>
+          <t>wetland:IEEXG0060</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr"/>
@@ -1558,12 +1558,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>IEEXG006J</t>
+          <t>upland:IEEXG006J</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr"/>
@@ -1610,12 +1610,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>IEEXG006M</t>
+          <t>transition:IEEXG006M</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
@@ -1662,12 +1662,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>IEEXG006G</t>
+          <t>wetland:IEEXG006G</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr"/>
@@ -1714,12 +1714,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>IEEXG006Z</t>
+          <t>upland:IEEXG006Z</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr"/>
@@ -1766,12 +1766,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0072</t>
+          <t>transition:IEEXG0072</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr"/>
@@ -1818,12 +1818,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>IEEXG006W</t>
+          <t>wetland:IEEXG006W</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr"/>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>IEEXG007F</t>
+          <t>upland:IEEXG007F</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr"/>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>IEEXG007I</t>
+          <t>transition:IEEXG007I</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr"/>
@@ -1974,12 +1974,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>IEEXG007C</t>
+          <t>wetland:IEEXG007C</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr"/>
@@ -2026,12 +2026,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>IEEXG008B</t>
+          <t>upland:IEEXG008B</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr"/>
@@ -2078,12 +2078,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>IEEXG008E</t>
+          <t>transition:IEEXG008E</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr"/>
@@ -2130,12 +2130,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0088</t>
+          <t>wetland:IEEXG0088</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr"/>
@@ -2182,12 +2182,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>IEEXG008R</t>
+          <t>upland:IEEXG008R</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr"/>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0097</t>
+          <t>upland:IEEXG0097</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr"/>
@@ -2286,12 +2286,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>IEEXG009A</t>
+          <t>transition:IEEXG009A</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr"/>
@@ -2338,12 +2338,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>IEEXG0094</t>
+          <t>wetland:IEEXG0094</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr"/>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>IEEXG009N</t>
+          <t>upland:IEEXG009N</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr"/>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>IEEXG009Q</t>
+          <t>transition:IEEXG009Q</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr"/>
@@ -2494,12 +2494,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>IEEXG009K</t>
+          <t>wetland:IEEXG009K</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr"/>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00A3</t>
+          <t>upland:IEEXG00A3</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr"/>
@@ -2598,12 +2598,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00A0</t>
+          <t>wetland:IEEXG00A0</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr"/>
@@ -2650,12 +2650,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00AJ</t>
+          <t>upland:IEEXG00AJ</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr"/>
@@ -2702,12 +2702,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00AM</t>
+          <t>transition:IEEXG00AM</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr"/>
@@ -2754,12 +2754,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00AZ</t>
+          <t>upland:IEEXG00AZ</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr"/>
@@ -2806,12 +2806,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00B2</t>
+          <t>transition:IEEXG00B2</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr"/>
@@ -2858,12 +2858,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00AW</t>
+          <t>wetland:IEEXG00AW</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr"/>
@@ -2910,12 +2910,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00BF</t>
+          <t>upland:IEEXG00BF</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr"/>
@@ -2962,12 +2962,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00BI</t>
+          <t>transition:IEEXG00BI</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr"/>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00BC</t>
+          <t>wetland:IEEXG00BC</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr"/>
@@ -3066,12 +3066,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00CR</t>
+          <t>upland:IEEXG00CR</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr"/>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00CU</t>
+          <t>transition:IEEXG00CU</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr"/>
@@ -3170,12 +3170,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00CO</t>
+          <t>wetland:IEEXG00CO</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr"/>
@@ -3222,12 +3222,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00D7</t>
+          <t>upland:IEEXG00D7</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr"/>
@@ -3274,12 +3274,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00D4</t>
+          <t>wetland:IEEXG00D4</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr"/>
@@ -3326,12 +3326,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00EJ</t>
+          <t>upland:IEEXG00EJ</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr"/>
@@ -3378,12 +3378,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00EG</t>
+          <t>wetland:IEEXG00EG</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr"/>
@@ -3430,12 +3430,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00EZ</t>
+          <t>upland:IEEXG00EZ</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr"/>
@@ -3482,12 +3482,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00F2</t>
+          <t>transition:IEEXG00F2</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr"/>
@@ -3534,12 +3534,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00EW</t>
+          <t>wetland:IEEXG00EW</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr"/>
@@ -3586,12 +3586,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00FF</t>
+          <t>upland:IEEXG00FF</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr"/>
@@ -3638,12 +3638,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00FI</t>
+          <t>transition:IEEXG00FI</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr"/>
@@ -3690,12 +3690,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00FC</t>
+          <t>wetland:IEEXG00FC</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr"/>
@@ -3742,12 +3742,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00FV</t>
+          <t>upland:IEEXG00FV</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr"/>
@@ -3794,12 +3794,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00FY</t>
+          <t>transition:IEEXG00FY</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr"/>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00FS</t>
+          <t>wetland:IEEXG00FS</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr"/>
@@ -3898,12 +3898,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00G8</t>
+          <t>wetland:IEEXG00G8</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr"/>
@@ -3950,12 +3950,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00GR</t>
+          <t>upland:IEEXG00GR</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr"/>
@@ -4002,12 +4002,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00GO</t>
+          <t>wetland:IEEXG00GO</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr"/>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00H7</t>
+          <t>upland:IEEXG00H7</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr"/>
@@ -4106,12 +4106,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00HA</t>
+          <t>transition:IEEXG00HA</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr"/>
@@ -4158,12 +4158,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00H4</t>
+          <t>wetland:IEEXG00H4</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr"/>
@@ -4210,12 +4210,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00HN</t>
+          <t>upland:IEEXG00HN</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr"/>
@@ -4262,12 +4262,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00HQ</t>
+          <t>transition:IEEXG00HQ</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr"/>
@@ -4314,12 +4314,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00HK</t>
+          <t>wetland:IEEXG00HK</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr"/>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00I3</t>
+          <t>upland:IEEXG00I3</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr"/>
@@ -4418,12 +4418,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00I6</t>
+          <t>transition:IEEXG00I6</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr"/>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00I0</t>
+          <t>wetland:IEEXG00I0</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr"/>
@@ -4522,12 +4522,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00IJ</t>
+          <t>upland:IEEXG00IJ</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr"/>
@@ -4574,12 +4574,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00IM</t>
+          <t>transition:IEEXG00IM</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr"/>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00IG</t>
+          <t>wetland:IEEXG00IG</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr"/>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00JF</t>
+          <t>upland:IEEXG00JF</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr"/>
@@ -4730,12 +4730,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00JI</t>
+          <t>transition:IEEXG00JI</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr"/>
@@ -4782,12 +4782,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00JC</t>
+          <t>wetland:IEEXG00JC</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr"/>
@@ -4834,12 +4834,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00JV</t>
+          <t>upland:IEEXG00JV</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr"/>
@@ -4886,12 +4886,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00JY</t>
+          <t>transition:IEEXG00JY</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr"/>
@@ -4938,12 +4938,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00JS</t>
+          <t>wetland:IEEXG00JS</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr"/>
@@ -4990,12 +4990,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00KB</t>
+          <t>upland:IEEXG00KB</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr"/>
@@ -5042,12 +5042,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00K8</t>
+          <t>wetland:IEEXG00K8</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr"/>
@@ -5094,12 +5094,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00KR</t>
+          <t>upland:IEEXG00KR</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr"/>
@@ -5146,12 +5146,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00KU</t>
+          <t>transition:IEEXG00KU</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr"/>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00KO</t>
+          <t>wetland:IEEXG00KO</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr"/>
@@ -5250,12 +5250,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00L7</t>
+          <t>upland:IEEXG00L7</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr"/>
@@ -5302,12 +5302,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00LA</t>
+          <t>transition:IEEXG00LA</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr"/>
@@ -5354,12 +5354,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00L4</t>
+          <t>wetland:IEEXG00L4</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr"/>
@@ -5406,12 +5406,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00LN</t>
+          <t>upland:IEEXG00LN</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr"/>
@@ -5458,12 +5458,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00LQ</t>
+          <t>transition:IEEXG00LQ</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr"/>
@@ -5510,12 +5510,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00LK</t>
+          <t>wetland:IEEXG00LK</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr"/>
@@ -5562,12 +5562,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00M6</t>
+          <t>transition:IEEXG00M6</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr"/>
@@ -5614,12 +5614,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00M0</t>
+          <t>wetland:IEEXG00M0</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr"/>
@@ -5666,12 +5666,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00MJ</t>
+          <t>upland:IEEXG00MJ</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr"/>
@@ -5718,12 +5718,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00MM</t>
+          <t>transition:IEEXG00MM</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr"/>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00MG</t>
+          <t>wetland:IEEXG00MG</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr"/>
@@ -5822,12 +5822,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00MZ</t>
+          <t>upland:IEEXG00MZ</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr"/>
@@ -5874,12 +5874,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00N2</t>
+          <t>transition:IEEXG00N2</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr"/>
@@ -5926,12 +5926,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00NF</t>
+          <t>upland:IEEXG00NF</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr"/>
@@ -5978,12 +5978,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00NI</t>
+          <t>transition:IEEXG00NI</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr"/>
@@ -6030,12 +6030,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00NC</t>
+          <t>wetland:IEEXG00NC</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr"/>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00NV</t>
+          <t>upland:IEEXG00NV</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr"/>
@@ -6134,12 +6134,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00NY</t>
+          <t>transition:IEEXG00NY</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr"/>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00NS</t>
+          <t>wetland:IEEXG00NS</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr"/>
@@ -6238,12 +6238,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00OB</t>
+          <t>upland:IEEXG00OB</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr"/>
@@ -6290,12 +6290,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00OR</t>
+          <t>upland:IEEXG00OR</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr"/>
@@ -6342,12 +6342,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00OU</t>
+          <t>transition:IEEXG00OU</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr"/>
@@ -6394,12 +6394,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00OO</t>
+          <t>wetland:IEEXG00OO</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr"/>
@@ -6446,12 +6446,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00PN</t>
+          <t>upland:IEEXG00PN</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr"/>
@@ -6498,12 +6498,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00PQ</t>
+          <t>transition:IEEXG00PQ</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr"/>
@@ -6550,12 +6550,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00PK</t>
+          <t>wetland:IEEXG00PK</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr"/>
@@ -6602,12 +6602,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00Q3</t>
+          <t>upland:IEEXG00Q3</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr"/>
@@ -6654,12 +6654,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00Q6</t>
+          <t>transition:IEEXG00Q6</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr"/>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00Q0</t>
+          <t>wetland:IEEXG00Q0</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr"/>
@@ -6758,12 +6758,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00QZ</t>
+          <t>upland:IEEXG00QZ</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr"/>
@@ -6810,12 +6810,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00R2</t>
+          <t>transition:IEEXG00R2</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr"/>
@@ -6862,12 +6862,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00QW</t>
+          <t>wetland:IEEXG00QW</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr"/>
@@ -6914,12 +6914,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00RF</t>
+          <t>upland:IEEXG00RF</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr"/>
@@ -6966,12 +6966,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00RI</t>
+          <t>transition:IEEXG00RI</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr"/>
@@ -7018,12 +7018,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>IEEXG00RC</t>
+          <t>wetland:IEEXG00RC</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>igsn</t>
+          <t>transect_location:igsn</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr"/>
